--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_visits_all.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_visits_all.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,17 +367,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mean_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_exposed</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>sd_visits</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>se_visits</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
@@ -391,13 +406,22 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>34155</v>
+      </c>
+      <c r="D2">
         <v>1.491484716157205</v>
       </c>
-      <c r="D2">
-        <v>34155</v>
-      </c>
       <c r="E2">
-        <v>5.851224124841342E-05</v>
+        <v>1.99848559983956</v>
+      </c>
+      <c r="F2">
+        <v>0.01081368908140476</v>
+      </c>
+      <c r="G2">
+        <v>1.470289523893402</v>
+      </c>
+      <c r="H2">
+        <v>1.512679908421009</v>
       </c>
     </row>
     <row r="3">
@@ -410,13 +434,22 @@
         <v>2</v>
       </c>
       <c r="C3">
+        <v>24352</v>
+      </c>
+      <c r="D3">
         <v>1.063406113537118</v>
       </c>
-      <c r="D3">
-        <v>24352</v>
-      </c>
       <c r="E3">
-        <v>7.426832394397058E-05</v>
+        <v>1.808582224683572</v>
+      </c>
+      <c r="F3">
+        <v>0.01158966654145435</v>
+      </c>
+      <c r="G3">
+        <v>1.040689655404074</v>
+      </c>
+      <c r="H3">
+        <v>1.086122571670162</v>
       </c>
     </row>
     <row r="4">
@@ -429,13 +462,22 @@
         <v>3</v>
       </c>
       <c r="C4">
+        <v>16561</v>
+      </c>
+      <c r="D4">
         <v>0.7231877729257642</v>
       </c>
-      <c r="D4">
-        <v>16561</v>
-      </c>
       <c r="E4">
-        <v>8.392371522275471E-05</v>
+        <v>1.389860647804041</v>
+      </c>
+      <c r="F4">
+        <v>0.01080010505530477</v>
+      </c>
+      <c r="G4">
+        <v>0.7020184087284932</v>
+      </c>
+      <c r="H4">
+        <v>0.7443571371230352</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +490,22 @@
         <v>4</v>
       </c>
       <c r="C5">
+        <v>11615</v>
+      </c>
+      <c r="D5">
         <v>0.5072052401746725</v>
       </c>
-      <c r="D5">
-        <v>11615</v>
-      </c>
       <c r="E5">
-        <v>0.0001034105896785683</v>
+        <v>1.201113999116571</v>
+      </c>
+      <c r="F5">
+        <v>0.01114486011216955</v>
+      </c>
+      <c r="G5">
+        <v>0.4853594390639613</v>
+      </c>
+      <c r="H5">
+        <v>0.5290510412853836</v>
       </c>
     </row>
     <row r="6">
@@ -467,13 +518,22 @@
         <v>5</v>
       </c>
       <c r="C6">
+        <v>8863</v>
+      </c>
+      <c r="D6">
         <v>0.3870305676855895</v>
       </c>
-      <c r="D6">
-        <v>8863</v>
-      </c>
       <c r="E6">
-        <v>0.0001092431267487753</v>
+        <v>0.9682218323743959</v>
+      </c>
+      <c r="F6">
+        <v>0.01028453111984244</v>
+      </c>
+      <c r="G6">
+        <v>0.3668705036541807</v>
+      </c>
+      <c r="H6">
+        <v>0.4071906317169983</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +546,22 @@
         <v>6</v>
       </c>
       <c r="C7">
+        <v>7101</v>
+      </c>
+      <c r="D7">
         <v>0.3100873362445415</v>
       </c>
-      <c r="D7">
-        <v>7101</v>
-      </c>
       <c r="E7">
-        <v>0.0001194426687582443</v>
+        <v>0.8481623908522931</v>
+      </c>
+      <c r="F7">
+        <v>0.01006512689953639</v>
+      </c>
+      <c r="G7">
+        <v>0.290356686470537</v>
+      </c>
+      <c r="H7">
+        <v>0.3298179860185459</v>
       </c>
     </row>
     <row r="8">
@@ -505,13 +574,22 @@
         <v>7</v>
       </c>
       <c r="C8">
+        <v>5961</v>
+      </c>
+      <c r="D8">
         <v>0.2603056768558952</v>
       </c>
-      <c r="D8">
-        <v>5961</v>
-      </c>
       <c r="E8">
-        <v>0.0001319055627513995</v>
+        <v>0.7862890595610924</v>
+      </c>
+      <c r="F8">
+        <v>0.01018410039653354</v>
+      </c>
+      <c r="G8">
+        <v>0.2403411524556905</v>
+      </c>
+      <c r="H8">
+        <v>0.2802702012560999</v>
       </c>
     </row>
     <row r="9">
@@ -524,13 +602,22 @@
         <v>8</v>
       </c>
       <c r="C9">
+        <v>5119</v>
+      </c>
+      <c r="D9">
         <v>0.2235371179039301</v>
       </c>
-      <c r="D9">
-        <v>5119</v>
-      </c>
       <c r="E9">
-        <v>0.0001413844189399481</v>
+        <v>0.7237468405535942</v>
+      </c>
+      <c r="F9">
+        <v>0.01011565749278282</v>
+      </c>
+      <c r="G9">
+        <v>0.2037061036860692</v>
+      </c>
+      <c r="H9">
+        <v>0.2433681321217911</v>
       </c>
     </row>
     <row r="10">
@@ -543,13 +630,22 @@
         <v>9</v>
       </c>
       <c r="C10">
+        <v>4574</v>
+      </c>
+      <c r="D10">
         <v>0.1997379912663755</v>
       </c>
-      <c r="D10">
-        <v>4574</v>
-      </c>
       <c r="E10">
-        <v>0.0001420750328196961</v>
+        <v>0.6498512001172898</v>
+      </c>
+      <c r="F10">
+        <v>0.009608726793107546</v>
+      </c>
+      <c r="G10">
+        <v>0.1809002469327055</v>
+      </c>
+      <c r="H10">
+        <v>0.2185757356000456</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +658,22 @@
         <v>10</v>
       </c>
       <c r="C11">
+        <v>4364</v>
+      </c>
+      <c r="D11">
         <v>0.1905676855895196</v>
       </c>
-      <c r="D11">
-        <v>4364</v>
-      </c>
       <c r="E11">
-        <v>0.000147192362485183</v>
+        <v>0.6423474698853389</v>
+      </c>
+      <c r="F11">
+        <v>0.00972361258117594</v>
+      </c>
+      <c r="G11">
+        <v>0.1715044667195964</v>
+      </c>
+      <c r="H11">
+        <v>0.2096309044594429</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +686,22 @@
         <v>11</v>
       </c>
       <c r="C12">
+        <v>4062</v>
+      </c>
+      <c r="D12">
         <v>0.1773799126637555</v>
       </c>
-      <c r="D12">
-        <v>4062</v>
-      </c>
       <c r="E12">
-        <v>0.0001705300527476403</v>
+        <v>0.6926930742609148</v>
+      </c>
+      <c r="F12">
+        <v>0.01086853193819841</v>
+      </c>
+      <c r="G12">
+        <v>0.1560716306846917</v>
+      </c>
+      <c r="H12">
+        <v>0.1986881946428193</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +714,22 @@
         <v>12</v>
       </c>
       <c r="C13">
+        <v>4149</v>
+      </c>
+      <c r="D13">
         <v>0.18117903930131</v>
       </c>
-      <c r="D13">
-        <v>4149</v>
-      </c>
       <c r="E13">
-        <v>0.0001543843803936391</v>
+        <v>0.6405407942532086</v>
+      </c>
+      <c r="F13">
+        <v>0.009944319666906887</v>
+      </c>
+      <c r="G13">
+        <v>0.161682842043361</v>
+      </c>
+      <c r="H13">
+        <v>0.2006752365592591</v>
       </c>
     </row>
     <row r="14">
@@ -619,13 +742,22 @@
         <v>13</v>
       </c>
       <c r="C14">
+        <v>3559</v>
+      </c>
+      <c r="D14">
         <v>0.1554148471615721</v>
       </c>
-      <c r="D14">
-        <v>3559</v>
-      </c>
       <c r="E14">
-        <v>0.0001569389653315678</v>
+        <v>0.5585457776150499</v>
+      </c>
+      <c r="F14">
+        <v>0.009362563560757379</v>
+      </c>
+      <c r="G14">
+        <v>0.1370583152687774</v>
+      </c>
+      <c r="H14">
+        <v>0.1737713790543667</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +770,22 @@
         <v>14</v>
       </c>
       <c r="C15">
+        <v>3515</v>
+      </c>
+      <c r="D15">
         <v>0.1534934497816594</v>
       </c>
-      <c r="D15">
-        <v>3515</v>
-      </c>
       <c r="E15">
-        <v>0.0001588099541330477</v>
+        <v>0.5582169887776627</v>
+      </c>
+      <c r="F15">
+        <v>0.009415434901483236</v>
+      </c>
+      <c r="G15">
+        <v>0.1350331780440106</v>
+      </c>
+      <c r="H15">
+        <v>0.1719537215193082</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +798,22 @@
         <v>15</v>
       </c>
       <c r="C16">
+        <v>3335</v>
+      </c>
+      <c r="D16">
         <v>0.1456331877729258</v>
       </c>
-      <c r="D16">
-        <v>3335</v>
-      </c>
       <c r="E16">
-        <v>0.0001695239536328432</v>
+        <v>0.5653623853655321</v>
+      </c>
+      <c r="F16">
+        <v>0.009789916588125768</v>
+      </c>
+      <c r="G16">
+        <v>0.1264383354539257</v>
+      </c>
+      <c r="H16">
+        <v>0.1648280400919258</v>
       </c>
     </row>
     <row r="17">
@@ -676,13 +826,22 @@
         <v>16</v>
       </c>
       <c r="C17">
+        <v>3331</v>
+      </c>
+      <c r="D17">
         <v>0.1454585152838428</v>
       </c>
-      <c r="D17">
-        <v>3331</v>
-      </c>
       <c r="E17">
-        <v>0.0001823286550001989</v>
+        <v>0.6073367498056624</v>
+      </c>
+      <c r="F17">
+        <v>0.01052306479711394</v>
+      </c>
+      <c r="G17">
+        <v>0.1248261880295876</v>
+      </c>
+      <c r="H17">
+        <v>0.166090842538098</v>
       </c>
     </row>
     <row r="18">
@@ -695,13 +854,22 @@
         <v>17</v>
       </c>
       <c r="C18">
+        <v>3231</v>
+      </c>
+      <c r="D18">
         <v>0.1410917030567685</v>
       </c>
-      <c r="D18">
-        <v>3231</v>
-      </c>
       <c r="E18">
-        <v>0.000177918233786493</v>
+        <v>0.574853813364159</v>
+      </c>
+      <c r="F18">
+        <v>0.01011320795589517</v>
+      </c>
+      <c r="G18">
+        <v>0.1212627493197965</v>
+      </c>
+      <c r="H18">
+        <v>0.1609206567937406</v>
       </c>
     </row>
     <row r="19">
@@ -714,13 +882,22 @@
         <v>18</v>
       </c>
       <c r="C19">
+        <v>2994</v>
+      </c>
+      <c r="D19">
         <v>0.1307423580786026</v>
       </c>
-      <c r="D19">
-        <v>2994</v>
-      </c>
       <c r="E19">
-        <v>0.0001816688254016082</v>
+        <v>0.5439164632524151</v>
+      </c>
+      <c r="F19">
+        <v>0.009940455975238925</v>
+      </c>
+      <c r="G19">
+        <v>0.111251540374307</v>
+      </c>
+      <c r="H19">
+        <v>0.1502331757828983</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +910,22 @@
         <v>19</v>
       </c>
       <c r="C20">
+        <v>2932</v>
+      </c>
+      <c r="D20">
         <v>0.1280349344978166</v>
       </c>
-      <c r="D20">
-        <v>2932</v>
-      </c>
       <c r="E20">
-        <v>0.0001962881859303481</v>
+        <v>0.5755169611477805</v>
+      </c>
+      <c r="F20">
+        <v>0.01062860199065919</v>
+      </c>
+      <c r="G20">
+        <v>0.1071946513972684</v>
+      </c>
+      <c r="H20">
+        <v>0.1488752175983648</v>
       </c>
     </row>
     <row r="21">
@@ -752,13 +938,22 @@
         <v>20</v>
       </c>
       <c r="C21">
+        <v>2811</v>
+      </c>
+      <c r="D21">
         <v>0.1227510917030568</v>
       </c>
-      <c r="D21">
-        <v>2811</v>
-      </c>
       <c r="E21">
-        <v>0.0001858825101818302</v>
+        <v>0.5225157361211248</v>
+      </c>
+      <c r="F21">
+        <v>0.009855279632750229</v>
+      </c>
+      <c r="G21">
+        <v>0.1034267749714713</v>
+      </c>
+      <c r="H21">
+        <v>0.1420754084346422</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +966,22 @@
         <v>21</v>
       </c>
       <c r="C22">
+        <v>2769</v>
+      </c>
+      <c r="D22">
         <v>0.1209170305676856</v>
       </c>
-      <c r="D22">
-        <v>2769</v>
-      </c>
       <c r="E22">
-        <v>0.0001995321987689213</v>
+        <v>0.5525046583911432</v>
+      </c>
+      <c r="F22">
+        <v>0.01049964139001216</v>
+      </c>
+      <c r="G22">
+        <v>0.100329109169602</v>
+      </c>
+      <c r="H22">
+        <v>0.1415049519657692</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +994,22 @@
         <v>22</v>
       </c>
       <c r="C23">
+        <v>2515</v>
+      </c>
+      <c r="D23">
         <v>0.109825327510917</v>
       </c>
-      <c r="D23">
-        <v>2515</v>
-      </c>
       <c r="E23">
-        <v>0.0002022166417344546</v>
+        <v>0.5085748539621533</v>
+      </c>
+      <c r="F23">
+        <v>0.01014111922022502</v>
+      </c>
+      <c r="G23">
+        <v>0.08993952514037849</v>
+      </c>
+      <c r="H23">
+        <v>0.1297111298814556</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +1022,22 @@
         <v>23</v>
       </c>
       <c r="C24">
+        <v>2496</v>
+      </c>
+      <c r="D24">
         <v>0.1089956331877729</v>
       </c>
-      <c r="D24">
-        <v>2496</v>
-      </c>
       <c r="E24">
-        <v>0.0002142723092128324</v>
+        <v>0.5348236837952297</v>
+      </c>
+      <c r="F24">
+        <v>0.01070504113717073</v>
+      </c>
+      <c r="G24">
+        <v>0.08800395478898032</v>
+      </c>
+      <c r="H24">
+        <v>0.1299873115865655</v>
       </c>
     </row>
     <row r="25">
@@ -828,13 +1050,22 @@
         <v>24</v>
       </c>
       <c r="C25">
+        <v>2296</v>
+      </c>
+      <c r="D25">
         <v>0.1002620087336245</v>
       </c>
-      <c r="D25">
-        <v>2296</v>
-      </c>
       <c r="E25">
-        <v>0.0002105570229625201</v>
+        <v>0.4834389247219462</v>
+      </c>
+      <c r="F25">
+        <v>0.01008917542585393</v>
+      </c>
+      <c r="G25">
+        <v>0.08047715398479174</v>
+      </c>
+      <c r="H25">
+        <v>0.1200468634824572</v>
       </c>
     </row>
     <row r="26">
@@ -847,13 +1078,22 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>34533</v>
+      </c>
+      <c r="D26">
         <v>1.494546870942612</v>
       </c>
-      <c r="D26">
-        <v>34533</v>
-      </c>
       <c r="E26">
-        <v>5.808700867121358E-05</v>
+        <v>2.005918670443019</v>
+      </c>
+      <c r="F26">
+        <v>0.01079434181429201</v>
+      </c>
+      <c r="G26">
+        <v>1.473389608177075</v>
+      </c>
+      <c r="H26">
+        <v>1.51570413370815</v>
       </c>
     </row>
     <row r="27">
@@ -866,13 +1106,22 @@
         <v>2</v>
       </c>
       <c r="C27">
+        <v>24577</v>
+      </c>
+      <c r="D27">
         <v>1.063663117804899</v>
       </c>
-      <c r="D27">
-        <v>24577</v>
-      </c>
       <c r="E27">
-        <v>7.292603026320322E-05</v>
+        <v>1.792303045778746</v>
+      </c>
+      <c r="F27">
+        <v>0.01143265262995829</v>
+      </c>
+      <c r="G27">
+        <v>1.04125442677832</v>
+      </c>
+      <c r="H27">
+        <v>1.086071808831479</v>
       </c>
     </row>
     <row r="28">
@@ -885,13 +1134,22 @@
         <v>3</v>
       </c>
       <c r="C28">
+        <v>16721</v>
+      </c>
+      <c r="D28">
         <v>0.7236648489569809</v>
       </c>
-      <c r="D28">
-        <v>16721</v>
-      </c>
       <c r="E28">
-        <v>8.165926671871307E-05</v>
+        <v>1.365424598803601</v>
+      </c>
+      <c r="F28">
+        <v>0.01055933575079394</v>
+      </c>
+      <c r="G28">
+        <v>0.7029674328958215</v>
+      </c>
+      <c r="H28">
+        <v>0.7443622650181403</v>
       </c>
     </row>
     <row r="29">
@@ -904,13 +1162,22 @@
         <v>4</v>
       </c>
       <c r="C29">
+        <v>11702</v>
+      </c>
+      <c r="D29">
         <v>0.5064485415043711</v>
       </c>
-      <c r="D29">
-        <v>11702</v>
-      </c>
       <c r="E29">
-        <v>0.0001016462401551876</v>
+        <v>1.189464302296005</v>
+      </c>
+      <c r="F29">
+        <v>0.01099566160479679</v>
+      </c>
+      <c r="G29">
+        <v>0.4848952112757924</v>
+      </c>
+      <c r="H29">
+        <v>0.5280018717329499</v>
       </c>
     </row>
     <row r="30">
@@ -923,13 +1190,22 @@
         <v>5</v>
       </c>
       <c r="C30">
+        <v>8950</v>
+      </c>
+      <c r="D30">
         <v>0.3873452782826972</v>
       </c>
-      <c r="D30">
-        <v>8950</v>
-      </c>
       <c r="E30">
-        <v>0.0001081247478544009</v>
+        <v>0.9677164932968878</v>
+      </c>
+      <c r="F30">
+        <v>0.01022908118221138</v>
+      </c>
+      <c r="G30">
+        <v>0.3672939356048692</v>
+      </c>
+      <c r="H30">
+        <v>0.4073966209605251</v>
       </c>
     </row>
     <row r="31">
@@ -942,13 +1218,22 @@
         <v>6</v>
       </c>
       <c r="C31">
+        <v>7129</v>
+      </c>
+      <c r="D31">
         <v>0.3085345797628322</v>
       </c>
-      <c r="D31">
-        <v>7129</v>
-      </c>
       <c r="E31">
-        <v>0.0001184433744444953</v>
+        <v>0.8443828164148067</v>
+      </c>
+      <c r="F31">
+        <v>0.01000057748828119</v>
+      </c>
+      <c r="G31">
+        <v>0.2889304792112091</v>
+      </c>
+      <c r="H31">
+        <v>0.3281386803144552</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +1246,22 @@
         <v>7</v>
       </c>
       <c r="C32">
+        <v>5973</v>
+      </c>
+      <c r="D32">
         <v>0.2585042846014022</v>
       </c>
-      <c r="D32">
-        <v>5973</v>
-      </c>
       <c r="E32">
-        <v>0.0001309210570152206</v>
+        <v>0.7819914735519123</v>
+      </c>
+      <c r="F32">
+        <v>0.01011825826386667</v>
+      </c>
+      <c r="G32">
+        <v>0.2386688427181804</v>
+      </c>
+      <c r="H32">
+        <v>0.2783397264846241</v>
       </c>
     </row>
     <row r="33">
@@ -980,13 +1274,22 @@
         <v>8</v>
       </c>
       <c r="C33">
+        <v>5155</v>
+      </c>
+      <c r="D33">
         <v>0.223102224530425</v>
       </c>
-      <c r="D33">
-        <v>5155</v>
-      </c>
       <c r="E33">
-        <v>0.0001399805022489022</v>
+        <v>0.7215994890930907</v>
+      </c>
+      <c r="F33">
+        <v>0.01005036610804811</v>
+      </c>
+      <c r="G33">
+        <v>0.2033992418998033</v>
+      </c>
+      <c r="H33">
+        <v>0.2428052071610467</v>
       </c>
     </row>
     <row r="34">
@@ -999,13 +1302,22 @@
         <v>9</v>
       </c>
       <c r="C34">
+        <v>4593</v>
+      </c>
+      <c r="D34">
         <v>0.1987795377823942</v>
       </c>
-      <c r="D34">
-        <v>4593</v>
-      </c>
       <c r="E34">
-        <v>0.0001409396642325411</v>
+        <v>0.6473358778200611</v>
+      </c>
+      <c r="F34">
+        <v>0.00955171718936635</v>
+      </c>
+      <c r="G34">
+        <v>0.1800535803132539</v>
+      </c>
+      <c r="H34">
+        <v>0.2175054952515345</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1330,22 @@
         <v>10</v>
       </c>
       <c r="C35">
+        <v>4379</v>
+      </c>
+      <c r="D35">
         <v>0.1895178741452437</v>
       </c>
-      <c r="D35">
-        <v>4379</v>
-      </c>
       <c r="E35">
-        <v>0.0001458064716201715</v>
+        <v>0.6384865392247311</v>
+      </c>
+      <c r="F35">
+        <v>0.009648599352306648</v>
+      </c>
+      <c r="G35">
+        <v>0.1706017372843205</v>
+      </c>
+      <c r="H35">
+        <v>0.2084340110061668</v>
       </c>
     </row>
     <row r="36">
@@ -1037,13 +1358,22 @@
         <v>11</v>
       </c>
       <c r="C36">
+        <v>4073</v>
+      </c>
+      <c r="D36">
         <v>0.1762745607201593</v>
       </c>
-      <c r="D36">
-        <v>4073</v>
-      </c>
       <c r="E36">
-        <v>0.0001686732099087683</v>
+        <v>0.6870059839584132</v>
+      </c>
+      <c r="F36">
+        <v>0.0107647342995913</v>
+      </c>
+      <c r="G36">
+        <v>0.155169796023635</v>
+      </c>
+      <c r="H36">
+        <v>0.1973793254166835</v>
       </c>
     </row>
     <row r="37">
@@ -1056,13 +1386,22 @@
         <v>12</v>
       </c>
       <c r="C37">
+        <v>4180</v>
+      </c>
+      <c r="D37">
         <v>0.1809053925387345</v>
       </c>
-      <c r="D37">
-        <v>4180</v>
-      </c>
       <c r="E37">
-        <v>0.0001531424617191004</v>
+        <v>0.6401354899858396</v>
+      </c>
+      <c r="F37">
+        <v>0.009901107249706671</v>
+      </c>
+      <c r="G37">
+        <v>0.1614939568115594</v>
+      </c>
+      <c r="H37">
+        <v>0.2003168282659096</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1414,22 @@
         <v>13</v>
       </c>
       <c r="C38">
+        <v>3556</v>
+      </c>
+      <c r="D38">
         <v>0.1538994200640526</v>
       </c>
-      <c r="D38">
-        <v>3556</v>
-      </c>
       <c r="E38">
-        <v>0.0001553688685461054</v>
+        <v>0.5524916965499507</v>
+      </c>
+      <c r="F38">
+        <v>0.009264988384994555</v>
+      </c>
+      <c r="G38">
+        <v>0.1357341918643987</v>
+      </c>
+      <c r="H38">
+        <v>0.1720646482637065</v>
       </c>
     </row>
     <row r="39">
@@ -1094,13 +1442,22 @@
         <v>14</v>
       </c>
       <c r="C39">
+        <v>3533</v>
+      </c>
+      <c r="D39">
         <v>0.1529040076170692</v>
       </c>
-      <c r="D39">
-        <v>3533</v>
-      </c>
       <c r="E39">
-        <v>0.0001576837292334653</v>
+        <v>0.5570966153818327</v>
+      </c>
+      <c r="F39">
+        <v>0.009372570184146334</v>
+      </c>
+      <c r="G39">
+        <v>0.1345278103965954</v>
+      </c>
+      <c r="H39">
+        <v>0.1712802048375429</v>
       </c>
     </row>
     <row r="40">
@@ -1113,13 +1470,22 @@
         <v>15</v>
       </c>
       <c r="C40">
+        <v>3356</v>
+      </c>
+      <c r="D40">
         <v>0.1452436596555007</v>
       </c>
-      <c r="D40">
-        <v>3356</v>
-      </c>
       <c r="E40">
-        <v>0.0001690711719742883</v>
+        <v>0.5674028531457116</v>
+      </c>
+      <c r="F40">
+        <v>0.009794460953156149</v>
+      </c>
+      <c r="G40">
+        <v>0.1260399409631591</v>
+      </c>
+      <c r="H40">
+        <v>0.1644473783478424</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1498,22 @@
         <v>16</v>
       </c>
       <c r="C41">
+        <v>3352</v>
+      </c>
+      <c r="D41">
         <v>0.1450705444473297</v>
       </c>
-      <c r="D41">
-        <v>3352</v>
-      </c>
       <c r="E41">
-        <v>0.0001799197677871706</v>
+        <v>0.6030910616225957</v>
+      </c>
+      <c r="F41">
+        <v>0.0104167175137687</v>
+      </c>
+      <c r="G41">
+        <v>0.124646776364238</v>
+      </c>
+      <c r="H41">
+        <v>0.1654943125304214</v>
       </c>
     </row>
     <row r="42">
@@ -1151,13 +1526,22 @@
         <v>17</v>
       </c>
       <c r="C42">
+        <v>3270</v>
+      </c>
+      <c r="D42">
         <v>0.1415216826798234</v>
       </c>
-      <c r="D42">
-        <v>3270</v>
-      </c>
       <c r="E42">
-        <v>0.0001757504171487656</v>
+        <v>0.5747038640764633</v>
+      </c>
+      <c r="F42">
+        <v>0.01005009670841261</v>
+      </c>
+      <c r="G42">
+        <v>0.1218165592091636</v>
+      </c>
+      <c r="H42">
+        <v>0.1612268061504833</v>
       </c>
     </row>
     <row r="43">
@@ -1170,13 +1554,22 @@
         <v>18</v>
       </c>
       <c r="C43">
+        <v>3010</v>
+      </c>
+      <c r="D43">
         <v>0.130269194148706</v>
       </c>
-      <c r="D43">
-        <v>3010</v>
-      </c>
       <c r="E43">
-        <v>0.0001802318136041307</v>
+        <v>0.5424977589484333</v>
+      </c>
+      <c r="F43">
+        <v>0.009888142139525132</v>
+      </c>
+      <c r="G43">
+        <v>0.1108809928666097</v>
+      </c>
+      <c r="H43">
+        <v>0.1496573954308022</v>
       </c>
     </row>
     <row r="44">
@@ -1189,13 +1582,22 @@
         <v>19</v>
       </c>
       <c r="C44">
+        <v>2943</v>
+      </c>
+      <c r="D44">
         <v>0.1273695144118411</v>
       </c>
-      <c r="D44">
-        <v>2943</v>
-      </c>
       <c r="E44">
-        <v>0.0001950852970386558</v>
+        <v>0.5741360291847639</v>
+      </c>
+      <c r="F44">
+        <v>0.01058326498742727</v>
+      </c>
+      <c r="G44">
+        <v>0.1066181589673338</v>
+      </c>
+      <c r="H44">
+        <v>0.1481208698563483</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1610,22 @@
         <v>20</v>
       </c>
       <c r="C45">
+        <v>2830</v>
+      </c>
+      <c r="D45">
         <v>0.1224790097810093</v>
       </c>
-      <c r="D45">
-        <v>2830</v>
-      </c>
       <c r="E45">
-        <v>0.0001847105470448725</v>
+        <v>0.5227308481369893</v>
+      </c>
+      <c r="F45">
+        <v>0.009826184453622551</v>
+      </c>
+      <c r="G45">
+        <v>0.103211798886856</v>
+      </c>
+      <c r="H45">
+        <v>0.1417462206751625</v>
       </c>
     </row>
     <row r="46">
@@ -1227,13 +1638,22 @@
         <v>21</v>
       </c>
       <c r="C46">
+        <v>2797</v>
+      </c>
+      <c r="D46">
         <v>0.1210508093135982</v>
       </c>
-      <c r="D46">
-        <v>2797</v>
-      </c>
       <c r="E46">
-        <v>0.0001973576015119124</v>
+        <v>0.5520092114288189</v>
+      </c>
+      <c r="F46">
+        <v>0.01043758659748861</v>
+      </c>
+      <c r="G46">
+        <v>0.1005846559382332</v>
+      </c>
+      <c r="H46">
+        <v>0.1415169626889632</v>
       </c>
     </row>
     <row r="47">
@@ -1246,13 +1666,22 @@
         <v>22</v>
       </c>
       <c r="C47">
+        <v>2500</v>
+      </c>
+      <c r="D47">
         <v>0.1081970051068986</v>
       </c>
-      <c r="D47">
-        <v>2500</v>
-      </c>
       <c r="E47">
-        <v>0.000200263967542426</v>
+        <v>0.5006599188560649</v>
+      </c>
+      <c r="F47">
+        <v>0.0100131983771213</v>
+      </c>
+      <c r="G47">
+        <v>0.08856198697933002</v>
+      </c>
+      <c r="H47">
+        <v>0.1278320232344673</v>
       </c>
     </row>
     <row r="48">
@@ -1265,13 +1694,22 @@
         <v>23</v>
       </c>
       <c r="C48">
+        <v>2499</v>
+      </c>
+      <c r="D48">
         <v>0.1081537263048559</v>
       </c>
-      <c r="D48">
-        <v>2499</v>
-      </c>
       <c r="E48">
-        <v>0.0002114389445782739</v>
+        <v>0.5283859225011065</v>
+      </c>
+      <c r="F48">
+        <v>0.01056983262798667</v>
+      </c>
+      <c r="G48">
+        <v>0.0874271924144632</v>
+      </c>
+      <c r="H48">
+        <v>0.1288802601952486</v>
       </c>
     </row>
     <row r="49">
@@ -1284,13 +1722,22 @@
         <v>24</v>
       </c>
       <c r="C49">
+        <v>2295</v>
+      </c>
+      <c r="D49">
         <v>0.09932485068813295</v>
       </c>
-      <c r="D49">
-        <v>2295</v>
-      </c>
       <c r="E49">
-        <v>0.0002087503262252804</v>
+        <v>0.4790819986870184</v>
+      </c>
+      <c r="F49">
+        <v>0.01000042616664782</v>
+      </c>
+      <c r="G49">
+        <v>0.07971402856513105</v>
+      </c>
+      <c r="H49">
+        <v>0.1189356728111348</v>
       </c>
     </row>
   </sheetData>
